--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488150_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488150_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2961</v>
+        <v>3.6397</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2564</v>
+        <v>3.4523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0397</v>
+        <v>0.1874</v>
       </c>
       <c r="G2" t="n">
         <v>2.307</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.308</v>
+        <v>-0.9644</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8207</v>
+        <v>-0.6249</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4872</v>
+        <v>-0.3395</v>
       </c>
       <c r="V2" t="n">
         <v>0.6294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.012</v>
+        <v>1.1105</v>
       </c>
       <c r="E4" t="n">
         <v>0.63</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382</v>
+        <v>0.4805</v>
       </c>
       <c r="G4" t="n">
         <v>1.4052</v>
@@ -766,13 +766,13 @@
         <v>0.3706</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7638</v>
+        <v>-0.6653</v>
       </c>
       <c r="T4" t="n">
         <v>-0.7113</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0525</v>
+        <v>0.046</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.1716</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8655</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3135</v>
+        <v>0.1716</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4738</v>
+        <v>0.1306</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3865</v>
+        <v>0.1306</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0873</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7773</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5285</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2488</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2511</v>
+        <v>0.1306</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.915</v>
+        <v>0.1306</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3361</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.914</v>
+        <v>0.041</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7000999999999999</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2139</v>
+        <v>0.041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.147</v>
+        <v>-0.6736</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.8862</v>
       </c>
       <c r="F7" t="n">
-        <v>0.147</v>
+        <v>-1.5597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1306</v>
+        <v>-1.4738</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1306</v>
+        <v>-0.3865</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.0873</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.7773</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.5285</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2488</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1306</v>
+        <v>-3.2511</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1306</v>
+        <v>-1.915</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.3361</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0164</v>
+        <v>-0.3115</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2791</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0164</v>
+        <v>-0.0324</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>A. MARQUEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9372</v>
+        <v>-1.0605</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9766</v>
+        <v>2.3096</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0394</v>
+        <v>-3.3701</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5286</v>
+        <v>-0.4081</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7729</v>
+        <v>-1.0179</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2443</v>
+        <v>0.6098</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2407</v>
+        <v>2.9418</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1885</v>
+        <v>1.5412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0522</v>
+        <v>1.4006</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7693</v>
+        <v>-3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9614</v>
+        <v>-2.5591</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1922</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P8" t="n">
         <v>0.9264</v>
@@ -1078,22 +1078,22 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2955</v>
+        <v>-1.2644</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6603</v>
+        <v>-0.9647</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9558</v>
+        <v>-0.2997</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6304999999999999</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARQUEZ MARQUEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3543</v>
+        <v>-1.7726</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0158</v>
+        <v>-2.2703</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3701</v>
+        <v>0.4977</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4081</v>
+        <v>-1.5286</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0179</v>
+        <v>-1.7729</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6098</v>
+        <v>0.2443</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9418</v>
+        <v>0.2407</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5412</v>
+        <v>0.1885</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4006</v>
+        <v>0.0522</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.35</v>
+        <v>-1.7693</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5591</v>
+        <v>-1.9614</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.1922</v>
       </c>
       <c r="P10" t="n">
         <v>0.9264</v>
@@ -1234,28 +1234,28 @@
         <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5582</v>
+        <v>-0.54</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2584</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2997</v>
+        <v>0.4141</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2589</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4707</v>
+        <v>-2.3704</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9141</v>
+        <v>-1.737</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5566</v>
+        <v>-0.6333</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0084</v>
+        <v>-0.3862</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2465</v>
+        <v>0.0946</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2381</v>
+        <v>-0.4808</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8635</v>
+        <v>-0.5255</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8635</v>
+        <v>0.0859</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1448</v>
+        <v>0.1393</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.383</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2381</v>
+        <v>0.1306</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6481</v>
+        <v>-0.1694</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2651</v>
+        <v>0.1156</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8877</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.616</v>
+        <v>-2.3974</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8349</v>
+        <v>-0.8162</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7811</v>
+        <v>-1.5812</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3862</v>
+        <v>-1.0084</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0946</v>
+        <v>-1.2465</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4808</v>
+        <v>0.2381</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5255</v>
+        <v>-0.8635</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0859</v>
+        <v>-0.8635</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1393</v>
+        <v>-0.1448</v>
       </c>
       <c r="N12" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.383</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1306</v>
+        <v>0.2381</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4151</v>
+        <v>-0.5748</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0321</v>
+        <v>-0.2898</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8764</v>
+        <v>-3.6056</v>
       </c>
       <c r="E13" t="n">
         <v>-2.0344</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.842</v>
+        <v>-1.5711</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6132</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0779</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>-0.8792</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1987</v>
+        <v>0.0721</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.8625</v>
+        <v>-7.5194</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.5905</v>
+        <v>-3.2967</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.272</v>
+        <v>-4.2227</v>
       </c>
       <c r="G14" t="n">
         <v>-4.3979</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7442</v>
+        <v>-1.4012</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.149</v>
+        <v>-0.8552</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5952</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8321</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.9795</v>
+        <v>-7.6118</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.0089</v>
+        <v>-4.7152</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9705</v>
+        <v>-2.8967</v>
       </c>
       <c r="G15" t="n">
         <v>-3.9713</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4878</v>
+        <v>-1.1201</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0943</v>
+        <v>-0.8005</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3935</v>
+        <v>-0.3196</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.1913</v>
+        <v>-21.1912</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.058000000000001</v>
+        <v>-6.058000000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.1331</v>
+        <v>-15.133</v>
       </c>
       <c r="G16" t="n">
         <v>-8.3264</v>
@@ -1690,10 +1690,10 @@
         <v>-15.3199</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.1841</v>
+        <v>-4.184099999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9262999999999999</v>
+        <v>0.926299999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-14.8227</v>
@@ -1702,13 +1702,13 @@
         <v>15.7496</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.1266</v>
+        <v>-8.1265</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.131500000000001</v>
+        <v>-7.131600000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9949000000000001</v>
+        <v>-0.9951000000000002</v>
       </c>
       <c r="V16" t="n">
         <v>-5.664899999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6481</v>
+        <v>5.9266</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4298</v>
+        <v>4.8926</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2184</v>
+        <v>1.0341</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0736</v>
+        <v>3.6751</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6743</v>
+        <v>1.5831</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6007</v>
+        <v>2.092</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2915</v>
+        <v>5.2527</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1671</v>
+        <v>2.5464</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1244</v>
+        <v>2.7063</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3651</v>
+        <v>-1.5775</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8414</v>
+        <v>-0.9633</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4763</v>
+        <v>-0.6143</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5746</v>
+        <v>0.8074</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9002</v>
+        <v>-0.0805</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6745</v>
+        <v>0.8879</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1471</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>4.091</v>
+        <v>1.5733</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9439</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0442</v>
+        <v>4.2536</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2071</v>
+        <v>2.8629</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8371</v>
+        <v>1.3907</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6751</v>
+        <v>-0.0736</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5831</v>
+        <v>-0.6743</v>
       </c>
       <c r="I18" t="n">
-        <v>2.092</v>
+        <v>0.6007</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2527</v>
+        <v>0.2915</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5464</v>
+        <v>0.1671</v>
       </c>
       <c r="L18" t="n">
-        <v>2.7063</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5775</v>
+        <v>-0.3651</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9633</v>
+        <v>-0.8414</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6143</v>
+        <v>0.4763</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0751</v>
+        <v>1.1801</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.766</v>
+        <v>0.3333</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6909</v>
+        <v>0.8468</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2589</v>
+        <v>3.1471</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5733</v>
+        <v>4.091</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1568</v>
+        <v>3.5961</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1779</v>
+        <v>2.8634</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9789</v>
+        <v>0.7327</v>
       </c>
       <c r="G19" t="n">
         <v>0.8731</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3954</v>
+        <v>0.8347</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5471</v>
+        <v>0.1384</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9426</v>
+        <v>0.6964</v>
       </c>
       <c r="V19" t="n">
         <v>1.8883</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6378</v>
+        <v>2.8566</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5111</v>
+        <v>3.0008</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1266</v>
+        <v>-0.1442</v>
       </c>
       <c r="G20" t="n">
         <v>2.6868</v>
@@ -2014,13 +2014,13 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4126</v>
+        <v>0.6314</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6566</v>
+        <v>-0.1669</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0692</v>
+        <v>0.7983</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5733</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5886</v>
+        <v>2.3916</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7892</v>
+        <v>1.8243</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3778</v>
+        <v>0.5673</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3045</v>
+        <v>1.5084</v>
       </c>
       <c r="H21" t="n">
-        <v>0.191</v>
+        <v>0.1538</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1136</v>
+        <v>1.3546</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8844</v>
+        <v>3.5935</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1165</v>
+        <v>0.9488</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7678</v>
+        <v>2.6447</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5798</v>
+        <v>-2.0851</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9255</v>
+        <v>-0.795</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3457</v>
+        <v>-1.2901</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1853</v>
+        <v>0.1853</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8394</v>
+        <v>0.6979</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8207</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6601</v>
+        <v>0.6143</v>
       </c>
       <c r="V21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5091</v>
+        <v>2.3648</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1388</v>
+        <v>-0.3975</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3704</v>
+        <v>2.7623</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5084</v>
+        <v>1.3045</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1538</v>
+        <v>0.191</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3546</v>
+        <v>1.1136</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5935</v>
+        <v>1.8844</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9488</v>
+        <v>1.1165</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6447</v>
+        <v>0.7678</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0851</v>
+        <v>-0.5798</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.795</v>
+        <v>-0.9255</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2901</v>
+        <v>0.3457</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1853</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1845</v>
+        <v>0.6155</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6019</v>
+        <v>-0.429</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4173</v>
+        <v>1.0445</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4865</v>
+        <v>1.8531</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1836</v>
+        <v>0.3061</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6701</v>
+        <v>1.547</v>
       </c>
       <c r="G23" t="n">
         <v>0.09959999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1281</v>
+        <v>0.4946</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.766</v>
+        <v>-0.2764</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8941</v>
+        <v>0.771</v>
       </c>
       <c r="V23" t="n">
         <v>1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1536</v>
+        <v>0.0562</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2079</v>
+        <v>0.012</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0543</v>
+        <v>0.0442</v>
       </c>
       <c r="G25" t="n">
         <v>-1.142</v>
@@ -2404,13 +2404,13 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1102</v>
+        <v>1.0129</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.5627</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3517</v>
+        <v>0.4501</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3687</v>
+        <v>-0.6666</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2158</v>
+        <v>-1.1044</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5845</v>
+        <v>0.4378</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1846</v>
+        <v>-0.743</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1519</v>
+        <v>-0.5188</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.3365</v>
+        <v>-0.2242</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6858</v>
+        <v>-0.639</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6016</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0842</v>
+        <v>-0.5699</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.8704</v>
+        <v>-0.104</v>
       </c>
       <c r="N26" t="n">
         <v>-0.4497</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.4207</v>
+        <v>0.3457</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.594</v>
+        <v>0.1853</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R26" t="n">
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7249</v>
+        <v>0.521</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6624</v>
+        <v>-0.1679</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0624</v>
+        <v>0.6889</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.315</v>
+        <v>-0.63</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5733</v>
+        <v>0.6289</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.8883</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9867</v>
+        <v>-1.7627</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1044</v>
+        <v>0.551</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1177</v>
+        <v>-2.3137</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.743</v>
+        <v>-0.1846</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5188</v>
+        <v>1.1519</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2242</v>
+        <v>-1.3365</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.639</v>
+        <v>1.6858</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.06909999999999999</v>
+        <v>1.6016</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5699</v>
+        <v>0.0842</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.104</v>
+        <v>-1.8704</v>
       </c>
       <c r="N27" t="n">
         <v>-0.4497</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3457</v>
+        <v>-1.4207</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1853</v>
+        <v>-2.594</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R27" t="n">
         <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>0.201</v>
+        <v>1.3309</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1679</v>
+        <v>0.9976</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3688</v>
+        <v>0.3333</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.63</v>
+        <v>-0.315</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6289</v>
+        <v>1.5733</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.2589</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="28">
@@ -2605,7 +2605,7 @@
         <v>8.326400000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>8.8643</v>
+        <v>8.864300000000002</v>
       </c>
       <c r="I28" t="n">
         <v>-0.5379999999999996</v>
@@ -2638,13 +2638,13 @@
         <v>14.823</v>
       </c>
       <c r="S28" t="n">
-        <v>8.1266</v>
+        <v>8.1264</v>
       </c>
       <c r="T28" t="n">
-        <v>0.9949999999999997</v>
+        <v>0.9949000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>7.131600000000001</v>
+        <v>7.131500000000001</v>
       </c>
       <c r="V28" t="n">
         <v>5.664899999999999</v>
